--- a/docs/assets/downloadable_resources/WbxOne2024LabDetails.xlsx
+++ b/docs/assets/downloadable_resources/WbxOne2024LabDetails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christno/Box Sync/WebexOne24/LabCSVFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F445657-C97B-5C4A-88A3-44B4D15CEBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D6272A-CDC5-934A-9F5D-4D38E0DB6EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" activeTab="2" xr2:uid="{E1AAE71F-4365-0D4E-BED6-00B4C2DAB0FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" xr2:uid="{E1AAE71F-4365-0D4E-BED6-00B4C2DAB0FE}"/>
   </bookViews>
   <sheets>
     <sheet name="LabDetails" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="245">
   <si>
     <t>password</t>
   </si>
@@ -771,6 +771,9 @@
   </si>
   <si>
     <t>[{"command": "xCommand UserManagement User Add Active: True Passphrase: WebexOne2024 PassphraseChangeRequired: False Role: Admin Role: Audit Role: User Role: Integrator Role:RoomControl ShellLogin: True Username: User408","command": "xConfiguration UserInterface CustomWallpaperOverlay: Off","command": "xConfiguration Standby Control: Off","command": "xConfiguration Standby Halfwake Mode: Manual"}]</t>
+  </si>
+  <si>
+    <t>Background</t>
   </si>
 </sst>
 </file>
@@ -792,12 +795,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -812,8 +833,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,773 +1172,808 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040543FE-F27D-774A-AF44-226445AE1115}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>103</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>104</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>171</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
       <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>105</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>106</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>174</v>
       </c>
-      <c r="G2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="H2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>67</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>107</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>108</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>175</v>
       </c>
-      <c r="G3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="H3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>68</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>109</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>110</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>176</v>
       </c>
-      <c r="G4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="H4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>69</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>111</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>112</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>177</v>
       </c>
-      <c r="G5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="H5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2"/>
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>113</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>114</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>178</v>
       </c>
-      <c r="G6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="H6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>71</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>115</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>116</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>179</v>
       </c>
-      <c r="G7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="H7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>117</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>118</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>180</v>
       </c>
-      <c r="G8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="H8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>119</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>120</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>181</v>
       </c>
-      <c r="G9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="H9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>74</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>121</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>122</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>182</v>
       </c>
-      <c r="G10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="H10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>75</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>123</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>124</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>183</v>
       </c>
-      <c r="G11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="H11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>76</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>125</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>126</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>184</v>
       </c>
-      <c r="G12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="H12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
+      <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>77</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>127</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>128</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>185</v>
       </c>
-      <c r="G13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="H13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>78</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>129</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>130</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>186</v>
       </c>
-      <c r="G14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="H14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>28</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>79</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>131</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>132</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>187</v>
       </c>
-      <c r="G15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="H15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+      <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>80</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>133</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>134</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>188</v>
       </c>
-      <c r="G16" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="H16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+      <c r="B17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>31</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>81</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>135</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>136</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>189</v>
       </c>
-      <c r="G17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="H17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>34</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>82</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>137</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>138</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>190</v>
       </c>
-      <c r="G18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="H18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="3"/>
+      <c r="B19" t="s">
         <v>35</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>139</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>140</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>191</v>
       </c>
-      <c r="G19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="H19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>38</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>84</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>141</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>142</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>192</v>
       </c>
-      <c r="G20" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="H20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" t="s">
         <v>39</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>85</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>143</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>144</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>193</v>
       </c>
-      <c r="G21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="H21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
+      <c r="B22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>42</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>86</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>145</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>146</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>194</v>
       </c>
-      <c r="G22" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="H22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+      <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>44</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>87</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>147</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>148</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>195</v>
       </c>
-      <c r="G23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="H23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" t="s">
         <v>45</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>46</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>88</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>149</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>150</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>196</v>
       </c>
-      <c r="G24" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="H24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="3"/>
+      <c r="B25" t="s">
         <v>47</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>89</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>151</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>152</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>197</v>
       </c>
-      <c r="G25" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="H25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+      <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>50</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>90</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>153</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>154</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>198</v>
       </c>
-      <c r="G26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="H26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>52</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>91</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>155</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>156</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>199</v>
       </c>
-      <c r="G27" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="H27" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" t="s">
         <v>53</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>54</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>92</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>157</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>158</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>200</v>
       </c>
-      <c r="G28" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="H28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>56</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>93</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>159</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>160</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>201</v>
       </c>
-      <c r="G29" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="H29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" t="s">
         <v>57</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>94</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>161</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>162</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>202</v>
       </c>
-      <c r="G30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="H30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="3"/>
+      <c r="B31" t="s">
         <v>59</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>60</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>95</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>163</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>164</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>203</v>
       </c>
-      <c r="G31" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="H31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" t="s">
         <v>61</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>62</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>96</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>165</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>166</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>204</v>
       </c>
-      <c r="G32" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="H32" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="B33" t="s">
         <v>63</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>64</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>97</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>167</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>168</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>205</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>173</v>
       </c>
     </row>

--- a/docs/assets/downloadable_resources/WbxOne2024LabDetails.xlsx
+++ b/docs/assets/downloadable_resources/WbxOne2024LabDetails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christno/Box Sync/WebexOne24/LabCSVFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D6272A-CDC5-934A-9F5D-4D38E0DB6EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18581180-DD2D-B648-87E9-1418A9E59D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" xr2:uid="{E1AAE71F-4365-0D4E-BED6-00B4C2DAB0FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="179">
   <si>
     <t>password</t>
   </si>
@@ -348,204 +348,6 @@
   </si>
   <si>
     <t>WebexOne 24</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Expiration</t>
-  </si>
-  <si>
-    <t>7682-9823-3708-1346</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:27.227Z</t>
-  </si>
-  <si>
-    <t>9061-7452-8538-6637</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:27.738Z</t>
-  </si>
-  <si>
-    <t>5215-3822-9832-2045</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:27.859Z</t>
-  </si>
-  <si>
-    <t>1972-5571-7249-4224</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:27.943Z</t>
-  </si>
-  <si>
-    <t>4335-3735-6566-3804</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:28.231Z</t>
-  </si>
-  <si>
-    <t>5559-7443-6678-3386</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:28.273Z</t>
-  </si>
-  <si>
-    <t>2763-8826-9764-5899</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:28.399Z</t>
-  </si>
-  <si>
-    <t>0813-1107-9239-3750</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:28.673Z</t>
-  </si>
-  <si>
-    <t>3183-1103-9354-7387</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:29.395Z</t>
-  </si>
-  <si>
-    <t>2030-7205-1369-6859</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:29.649Z</t>
-  </si>
-  <si>
-    <t>1238-8319-7636-3092</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:29.752Z</t>
-  </si>
-  <si>
-    <t>9067-2781-5017-3949</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:30.049Z</t>
-  </si>
-  <si>
-    <t>2961-1103-1223-3831</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:30.160Z</t>
-  </si>
-  <si>
-    <t>8853-7299-3128-9848</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:30.387Z</t>
-  </si>
-  <si>
-    <t>1746-0699-7180-1781</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:30.544Z</t>
-  </si>
-  <si>
-    <t>0178-7897-6058-0679</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:30.798Z</t>
-  </si>
-  <si>
-    <t>8055-2921-9013-6275</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:31.576Z</t>
-  </si>
-  <si>
-    <t>2297-1114-7115-4731</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:31.774Z</t>
-  </si>
-  <si>
-    <t>0393-9564-8612-6303</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:32.087Z</t>
-  </si>
-  <si>
-    <t>2227-0202-8080-7520</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:32.144Z</t>
-  </si>
-  <si>
-    <t>9290-7487-4672-2495</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:32.450Z</t>
-  </si>
-  <si>
-    <t>2340-8033-1426-8164</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:32.685Z</t>
-  </si>
-  <si>
-    <t>8723-2117-6429-9322</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:32.826Z</t>
-  </si>
-  <si>
-    <t>1696-9448-7474-8227</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:33.007Z</t>
-  </si>
-  <si>
-    <t>4139-8859-8054-7638</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:33.964Z</t>
-  </si>
-  <si>
-    <t>6448-6423-7816-0104</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:34.091Z</t>
-  </si>
-  <si>
-    <t>3629-2224-7482-1443</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:34.171Z</t>
-  </si>
-  <si>
-    <t>6289-1640-6464-3648</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:34.530Z</t>
-  </si>
-  <si>
-    <t>1139-1858-3324-7754</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:34.611Z</t>
-  </si>
-  <si>
-    <t>1420-0249-1670-2757</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:34.855Z</t>
-  </si>
-  <si>
-    <t>0868-5191-6763-5480</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:34.955Z</t>
-  </si>
-  <si>
-    <t>2402-3203-3735-9296</t>
-  </si>
-  <si>
-    <t>2024-10-23T16:00:35.223Z</t>
   </si>
   <si>
     <t>DeviceID</t>
@@ -1172,20 +974,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040543FE-F27D-774A-AF44-226445AE1115}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="B1" t="s">
         <v>98</v>
@@ -1197,19 +997,13 @@
         <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>1</v>
@@ -1221,19 +1015,13 @@
         <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" t="s">
-        <v>174</v>
-      </c>
-      <c r="H2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" t="s">
         <v>4</v>
@@ -1245,19 +1033,13 @@
         <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" t="s">
         <v>5</v>
@@ -1269,19 +1051,13 @@
         <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
         <v>7</v>
@@ -1296,16 +1072,10 @@
         <v>111</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>9</v>
@@ -1317,19 +1087,13 @@
         <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" t="s">
         <v>11</v>
@@ -1341,19 +1105,13 @@
         <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
         <v>15</v>
@@ -1365,19 +1123,13 @@
         <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" t="s">
         <v>13</v>
@@ -1389,20 +1141,14 @@
         <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" t="s">
-        <v>181</v>
-      </c>
-      <c r="H9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -1413,20 +1159,14 @@
         <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>122</v>
-      </c>
-      <c r="G10" t="s">
-        <v>182</v>
-      </c>
-      <c r="H10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -1437,20 +1177,14 @@
         <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
-      </c>
-      <c r="G11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
       <c r="B12" t="s">
         <v>21</v>
       </c>
@@ -1461,20 +1195,14 @@
         <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
       <c r="B13" t="s">
         <v>23</v>
       </c>
@@ -1485,20 +1213,14 @@
         <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
       <c r="B14" t="s">
         <v>25</v>
       </c>
@@ -1509,20 +1231,14 @@
         <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
-      </c>
-      <c r="G14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
       <c r="B15" t="s">
         <v>27</v>
       </c>
@@ -1533,20 +1249,14 @@
         <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F15" t="s">
-        <v>132</v>
-      </c>
-      <c r="G15" t="s">
-        <v>187</v>
-      </c>
-      <c r="H15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -1557,20 +1267,14 @@
         <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G16" t="s">
-        <v>188</v>
-      </c>
-      <c r="H16" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
       <c r="B17" t="s">
         <v>32</v>
       </c>
@@ -1581,20 +1285,14 @@
         <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G17" t="s">
-        <v>189</v>
-      </c>
-      <c r="H17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
       <c r="B18" t="s">
         <v>33</v>
       </c>
@@ -1605,20 +1303,14 @@
         <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F18" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" t="s">
-        <v>190</v>
-      </c>
-      <c r="H18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
       <c r="B19" t="s">
         <v>35</v>
       </c>
@@ -1629,20 +1321,14 @@
         <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
-      </c>
-      <c r="G19" t="s">
-        <v>191</v>
-      </c>
-      <c r="H19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
       <c r="B20" t="s">
         <v>37</v>
       </c>
@@ -1653,20 +1339,14 @@
         <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G20" t="s">
-        <v>192</v>
-      </c>
-      <c r="H20" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
       <c r="B21" t="s">
         <v>39</v>
       </c>
@@ -1677,20 +1357,14 @@
         <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F21" t="s">
-        <v>144</v>
-      </c>
-      <c r="G21" t="s">
-        <v>193</v>
-      </c>
-      <c r="H21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
       <c r="B22" t="s">
         <v>41</v>
       </c>
@@ -1701,20 +1375,14 @@
         <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" t="s">
-        <v>194</v>
-      </c>
-      <c r="H22" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="3"/>
       <c r="B23" t="s">
         <v>43</v>
       </c>
@@ -1725,20 +1393,14 @@
         <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F23" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
       <c r="B24" t="s">
         <v>45</v>
       </c>
@@ -1749,20 +1411,14 @@
         <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F24" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" t="s">
-        <v>196</v>
-      </c>
-      <c r="H24" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
       <c r="B25" t="s">
         <v>47</v>
       </c>
@@ -1773,19 +1429,13 @@
         <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F25" t="s">
-        <v>152</v>
-      </c>
-      <c r="G25" t="s">
-        <v>197</v>
-      </c>
-      <c r="H25" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" t="s">
         <v>49</v>
@@ -1797,19 +1447,13 @@
         <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="F26" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" t="s">
-        <v>198</v>
-      </c>
-      <c r="H26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" t="s">
         <v>51</v>
@@ -1821,19 +1465,13 @@
         <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
-      </c>
-      <c r="G27" t="s">
-        <v>199</v>
-      </c>
-      <c r="H27" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" t="s">
         <v>53</v>
@@ -1845,19 +1483,13 @@
         <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
-      </c>
-      <c r="G28" t="s">
-        <v>200</v>
-      </c>
-      <c r="H28" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" t="s">
         <v>55</v>
@@ -1869,19 +1501,13 @@
         <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s">
-        <v>160</v>
-      </c>
-      <c r="G29" t="s">
-        <v>201</v>
-      </c>
-      <c r="H29" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" t="s">
         <v>57</v>
@@ -1893,19 +1519,13 @@
         <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="F30" t="s">
-        <v>162</v>
-      </c>
-      <c r="G30" t="s">
-        <v>202</v>
-      </c>
-      <c r="H30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
       <c r="B31" t="s">
         <v>59</v>
@@ -1917,19 +1537,13 @@
         <v>95</v>
       </c>
       <c r="E31" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="F31" t="s">
-        <v>164</v>
-      </c>
-      <c r="G31" t="s">
-        <v>203</v>
-      </c>
-      <c r="H31" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" t="s">
         <v>61</v>
@@ -1941,19 +1555,13 @@
         <v>96</v>
       </c>
       <c r="E32" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="F32" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" t="s">
-        <v>204</v>
-      </c>
-      <c r="H32" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" t="s">
         <v>63</v>
@@ -1965,16 +1573,10 @@
         <v>97</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="F33" t="s">
-        <v>168</v>
-      </c>
-      <c r="G33" t="s">
-        <v>205</v>
-      </c>
-      <c r="H33" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1996,170 +1598,170 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="D1" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D2" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D3" t="s">
-        <v>213</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D4" t="s">
-        <v>214</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D5" t="s">
-        <v>215</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D6" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
-        <v>217</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
-        <v>220</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
-        <v>221</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D12" t="s">
-        <v>222</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D13" t="s">
-        <v>223</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D14" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D17" t="s">
-        <v>227</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D18" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D19" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D21" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D22" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D23" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D24" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D25" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D26" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D27" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D28" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D29" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D30" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D31" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D32" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D33" t="s">
-        <v>243</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2850,233 +2452,233 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="B1" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C4" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C6" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C8" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C16" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C29" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C30" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C42" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
